--- a/tests/io/input_data_test/input_parameter_test.xlsx
+++ b/tests/io/input_data_test/input_parameter_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/pfas_modeling/reactormodels/tests/input_data_test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/pfas_modeling/reactormodels/tests/io/input_data_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2C4ABC-25BF-AB45-A756-347559DB0575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7331056-70C8-0041-A852-B3B37C1BC440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="680" windowWidth="27860" windowHeight="17500" activeTab="1" xr2:uid="{8FC1EBE6-09F5-E544-BEAB-0C438D750464}"/>
+    <workbookView xWindow="940" yWindow="680" windowWidth="27860" windowHeight="17500" xr2:uid="{8FC1EBE6-09F5-E544-BEAB-0C438D750464}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>water</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>porosity</t>
-  </si>
-  <si>
-    <t>bulk_density</t>
   </si>
   <si>
     <t>sorbent_mass</t>
@@ -700,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1156A5E6-1152-6E4D-AE94-8617611FAF4C}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -710,14 +707,14 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="2">
         <v>1</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -757,7 +754,7 @@
         <v>997</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -768,7 +765,7 @@
         <v>8.8999999999999995E-4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -779,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -802,124 +799,124 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3">
-        <v>500</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>30</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3">
-        <v>500</v>
+        <v>2.5000000000000001E-5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B14" s="3">
-        <v>2.5000000000000001E-5</v>
+        <v>5.0000000000000002E-5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="3">
-        <v>5.0000000000000002E-5</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A15" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
+      <c r="A16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>3</v>
+      <c r="A17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="6">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>32</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="C19" s="6"/>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" t="s">
-        <v>36</v>
+      <c r="A20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="3">
+        <v>500</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -928,19 +925,12 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -973,28 +963,28 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>25</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>27</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>28</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="10"/>
@@ -1017,7 +1007,7 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="7">
